--- a/data/nzd0561/nzd0561.xlsx
+++ b/data/nzd0561/nzd0561.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L487"/>
+  <dimension ref="A1:L488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20876,6 +20876,48 @@
       <c r="L487" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>411.89</v>
+      </c>
+      <c r="C488" t="n">
+        <v>311.83</v>
+      </c>
+      <c r="D488" t="n">
+        <v>313.05</v>
+      </c>
+      <c r="E488" t="n">
+        <v>324.49</v>
+      </c>
+      <c r="F488" t="n">
+        <v>330.9</v>
+      </c>
+      <c r="G488" t="n">
+        <v>328.84</v>
+      </c>
+      <c r="H488" t="n">
+        <v>329.06</v>
+      </c>
+      <c r="I488" t="n">
+        <v>327.63</v>
+      </c>
+      <c r="J488" t="n">
+        <v>325.88</v>
+      </c>
+      <c r="K488" t="n">
+        <v>326.98</v>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -20890,7 +20932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B506"/>
+  <dimension ref="A1:B507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25953,6 +25995,16 @@
       </c>
       <c r="B506" t="n">
         <v>0.44</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>0.68</v>
       </c>
     </row>
   </sheetData>
@@ -26121,28 +26173,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.791529624019222</v>
+        <v>2.802992764922045</v>
       </c>
       <c r="J2" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K2" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2537651149474579</v>
+        <v>0.2558488768778097</v>
       </c>
       <c r="M2" t="n">
-        <v>31.07498222509106</v>
+        <v>31.06009548622505</v>
       </c>
       <c r="N2" t="n">
-        <v>1351.009477511481</v>
+        <v>1350.080940749841</v>
       </c>
       <c r="O2" t="n">
-        <v>36.75608082360633</v>
+        <v>36.74344758933001</v>
       </c>
       <c r="P2" t="n">
-        <v>308.2138555952969</v>
+        <v>308.0987919652981</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26199,28 +26251,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01044416603699831</v>
+        <v>0.009888200988742856</v>
       </c>
       <c r="J3" t="n">
+        <v>487</v>
+      </c>
+      <c r="K3" t="n">
         <v>486</v>
       </c>
-      <c r="K3" t="n">
-        <v>485</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0003360284926885448</v>
+        <v>0.0003024044053397956</v>
       </c>
       <c r="M3" t="n">
-        <v>3.391569087239907</v>
+        <v>3.387405477735246</v>
       </c>
       <c r="N3" t="n">
-        <v>19.13272669323711</v>
+        <v>19.09773218403894</v>
       </c>
       <c r="O3" t="n">
-        <v>4.374097243230552</v>
+        <v>4.370095214527818</v>
       </c>
       <c r="P3" t="n">
-        <v>313.0212255779539</v>
+        <v>313.0267965265744</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26277,28 +26329,28 @@
         <v>0.1302</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01770309237006796</v>
+        <v>-0.01888000496567554</v>
       </c>
       <c r="J4" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K4" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001018812444021688</v>
+        <v>0.001162194723208332</v>
       </c>
       <c r="M4" t="n">
-        <v>3.392888965189627</v>
+        <v>3.391889747817077</v>
       </c>
       <c r="N4" t="n">
-        <v>18.0850793576516</v>
+        <v>18.06749084185317</v>
       </c>
       <c r="O4" t="n">
-        <v>4.252655565367551</v>
+        <v>4.250587117311345</v>
       </c>
       <c r="P4" t="n">
-        <v>316.6094438375889</v>
+        <v>316.6212452451449</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26355,28 +26407,28 @@
         <v>0.1707</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03528365617391441</v>
+        <v>-0.03579972134178739</v>
       </c>
       <c r="J5" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K5" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004586423330025124</v>
+        <v>0.004739448688319992</v>
       </c>
       <c r="M5" t="n">
-        <v>3.128662695361589</v>
+        <v>3.124721314699218</v>
       </c>
       <c r="N5" t="n">
-        <v>15.90141103585459</v>
+        <v>15.87251768148902</v>
       </c>
       <c r="O5" t="n">
-        <v>3.987657336815011</v>
+        <v>3.984032841416975</v>
       </c>
       <c r="P5" t="n">
-        <v>326.775479820306</v>
+        <v>326.7806546271644</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26433,28 +26485,28 @@
         <v>0.1817</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0465348034859075</v>
+        <v>-0.04646765262057014</v>
       </c>
       <c r="J6" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K6" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009666212797693419</v>
+        <v>0.009678448419150776</v>
       </c>
       <c r="M6" t="n">
-        <v>2.859953110041742</v>
+        <v>2.854456273233771</v>
       </c>
       <c r="N6" t="n">
-        <v>13.05690042115588</v>
+        <v>13.03015317272457</v>
       </c>
       <c r="O6" t="n">
-        <v>3.613433328727109</v>
+        <v>3.609730346261971</v>
       </c>
       <c r="P6" t="n">
-        <v>331.9522258758529</v>
+        <v>331.9515525253148</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26511,28 +26563,28 @@
         <v>0.1982</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04212271393008438</v>
+        <v>0.04296176397292852</v>
       </c>
       <c r="J7" t="n">
+        <v>487</v>
+      </c>
+      <c r="K7" t="n">
         <v>486</v>
       </c>
-      <c r="K7" t="n">
-        <v>485</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.007105930752180356</v>
+        <v>0.007415320906989264</v>
       </c>
       <c r="M7" t="n">
-        <v>3.084980560956976</v>
+        <v>3.082416747095079</v>
       </c>
       <c r="N7" t="n">
-        <v>14.60613813198466</v>
+        <v>14.58604003683263</v>
       </c>
       <c r="O7" t="n">
-        <v>3.821797761784977</v>
+        <v>3.819167453363708</v>
       </c>
       <c r="P7" t="n">
-        <v>325.5257393564075</v>
+        <v>325.5173259578459</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26589,28 +26641,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1003093466080414</v>
+        <v>0.1011185251827646</v>
       </c>
       <c r="J8" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K8" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04201816165208216</v>
+        <v>0.04281169389759576</v>
       </c>
       <c r="M8" t="n">
-        <v>3.103170168019049</v>
+        <v>3.100471273933103</v>
       </c>
       <c r="N8" t="n">
-        <v>13.57637124005483</v>
+        <v>13.55758466624281</v>
       </c>
       <c r="O8" t="n">
-        <v>3.684612766635706</v>
+        <v>3.682062555992607</v>
       </c>
       <c r="P8" t="n">
-        <v>324.2841370983749</v>
+        <v>324.2760342495561</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26667,28 +26719,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1776485104475591</v>
+        <v>0.1786474929454092</v>
       </c>
       <c r="J9" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K9" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1340170983602555</v>
+        <v>0.1356741406119889</v>
       </c>
       <c r="M9" t="n">
-        <v>2.762980192385939</v>
+        <v>2.761734264178812</v>
       </c>
       <c r="N9" t="n">
-        <v>12.04773364230687</v>
+        <v>12.03704789622298</v>
       </c>
       <c r="O9" t="n">
-        <v>3.470984535014074</v>
+        <v>3.469444897418459</v>
       </c>
       <c r="P9" t="n">
-        <v>320.3236669732736</v>
+        <v>320.3136664039119</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26745,28 +26797,28 @@
         <v>0.1446</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05100135596204515</v>
+        <v>0.05318669572191536</v>
       </c>
       <c r="J10" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K10" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L10" t="n">
-        <v>0.008467802485301545</v>
+        <v>0.009205846385148986</v>
       </c>
       <c r="M10" t="n">
-        <v>3.467262313301041</v>
+        <v>3.470837870346188</v>
       </c>
       <c r="N10" t="n">
-        <v>17.99420473999362</v>
+        <v>18.02484095863647</v>
       </c>
       <c r="O10" t="n">
-        <v>4.241957654196188</v>
+        <v>4.245567212827571</v>
       </c>
       <c r="P10" t="n">
-        <v>318.7822618269396</v>
+        <v>318.7603849252974</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26823,28 +26875,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0651826610583332</v>
+        <v>0.0667919059358954</v>
       </c>
       <c r="J11" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K11" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L11" t="n">
-        <v>0.009217792185355789</v>
+        <v>0.009701041417778722</v>
       </c>
       <c r="M11" t="n">
-        <v>4.032361200760572</v>
+        <v>4.031517188393082</v>
       </c>
       <c r="N11" t="n">
-        <v>26.87661301743536</v>
+        <v>26.85797089247516</v>
       </c>
       <c r="O11" t="n">
-        <v>5.184265909213702</v>
+        <v>5.182467645096799</v>
       </c>
       <c r="P11" t="n">
-        <v>321.0341598130913</v>
+        <v>321.0180232242501</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26882,7 +26934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L487"/>
+  <dimension ref="A1:L488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57027,6 +57079,68 @@
         </is>
       </c>
     </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>-46.777318645752345,168.53034392876617</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>-46.77650677697396,168.52932068439677</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>-46.77663868559575,168.52842235498997</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>-46.77690093310253,168.5275625256367</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>-46.77722654095907,168.52676676933385</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>-46.77758825214454,168.52602662469096</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>-46.77799778925423,168.52534281317511</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>-46.778457878159266,168.52473414089746</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>-46.77896786808213,168.5242099804355</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>-46.77950990329557,168.52377381407817</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0561/nzd0561.xlsx
+++ b/data/nzd0561/nzd0561.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L488"/>
+  <dimension ref="A1:L490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20916,6 +20916,90 @@
         <v>326.98</v>
       </c>
       <c r="L488" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:21:11+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>413.8</v>
+      </c>
+      <c r="C489" t="n">
+        <v>313.22</v>
+      </c>
+      <c r="D489" t="n">
+        <v>315.29</v>
+      </c>
+      <c r="E489" t="n">
+        <v>325.56</v>
+      </c>
+      <c r="F489" t="n">
+        <v>331.58</v>
+      </c>
+      <c r="G489" t="n">
+        <v>329.22</v>
+      </c>
+      <c r="H489" t="n">
+        <v>328.78</v>
+      </c>
+      <c r="I489" t="n">
+        <v>327.21</v>
+      </c>
+      <c r="J489" t="n">
+        <v>326.21</v>
+      </c>
+      <c r="K489" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:21:16+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>415.61</v>
+      </c>
+      <c r="C490" t="n">
+        <v>314.48</v>
+      </c>
+      <c r="D490" t="n">
+        <v>316.18</v>
+      </c>
+      <c r="E490" t="n">
+        <v>326.49</v>
+      </c>
+      <c r="F490" t="n">
+        <v>331.57</v>
+      </c>
+      <c r="G490" t="n">
+        <v>328.8</v>
+      </c>
+      <c r="H490" t="n">
+        <v>328.58</v>
+      </c>
+      <c r="I490" t="n">
+        <v>327.31</v>
+      </c>
+      <c r="J490" t="n">
+        <v>327.47</v>
+      </c>
+      <c r="K490" t="n">
+        <v>327.7</v>
+      </c>
+      <c r="L490" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -20932,7 +21016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B507"/>
+  <dimension ref="A1:B509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26005,6 +26089,26 @@
       </c>
       <c r="B507" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>-0.74</v>
       </c>
     </row>
   </sheetData>
@@ -26173,28 +26277,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.802992764922045</v>
+        <v>2.827623688354041</v>
       </c>
       <c r="J2" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K2" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2558488768778097</v>
+        <v>0.2601738239994342</v>
       </c>
       <c r="M2" t="n">
-        <v>31.06009548622505</v>
+        <v>31.03768108733989</v>
       </c>
       <c r="N2" t="n">
-        <v>1350.080940749841</v>
+        <v>1348.845397508032</v>
       </c>
       <c r="O2" t="n">
-        <v>36.74344758933001</v>
+        <v>36.72663063102893</v>
       </c>
       <c r="P2" t="n">
-        <v>308.0987919652981</v>
+        <v>307.8508476404879</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26251,28 +26355,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009888200988742856</v>
+        <v>0.01031240922509876</v>
       </c>
       <c r="J3" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K3" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0003024044053397956</v>
+        <v>0.0003315945115981433</v>
       </c>
       <c r="M3" t="n">
-        <v>3.387405477735246</v>
+        <v>3.376262953920083</v>
       </c>
       <c r="N3" t="n">
-        <v>19.09773218403894</v>
+        <v>19.02237855525441</v>
       </c>
       <c r="O3" t="n">
-        <v>4.370095214527818</v>
+        <v>4.361465184459737</v>
       </c>
       <c r="P3" t="n">
-        <v>313.0267965265744</v>
+        <v>313.0225311961323</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26329,28 +26433,28 @@
         <v>0.1302</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01888000496567554</v>
+        <v>-0.01917034177358425</v>
       </c>
       <c r="J4" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K4" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001162194723208332</v>
+        <v>0.001208080441461368</v>
       </c>
       <c r="M4" t="n">
-        <v>3.391889747817077</v>
+        <v>3.379757255171731</v>
       </c>
       <c r="N4" t="n">
-        <v>18.06749084185317</v>
+        <v>17.99500662540152</v>
       </c>
       <c r="O4" t="n">
-        <v>4.250587117311345</v>
+        <v>4.242052171461534</v>
       </c>
       <c r="P4" t="n">
-        <v>316.6212452451449</v>
+        <v>316.6241629607206</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26407,28 +26511,28 @@
         <v>0.1707</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03579972134178739</v>
+        <v>-0.03565631537011406</v>
       </c>
       <c r="J5" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K5" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004739448688319992</v>
+        <v>0.004740546922361477</v>
       </c>
       <c r="M5" t="n">
-        <v>3.124721314699218</v>
+        <v>3.113916087638571</v>
       </c>
       <c r="N5" t="n">
-        <v>15.87251768148902</v>
+        <v>15.80861849670142</v>
       </c>
       <c r="O5" t="n">
-        <v>3.984032841416975</v>
+        <v>3.976005344149002</v>
       </c>
       <c r="P5" t="n">
-        <v>326.7806546271644</v>
+        <v>326.7792106850609</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26485,28 +26589,28 @@
         <v>0.1817</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04646765262057014</v>
+        <v>-0.0458242076109281</v>
       </c>
       <c r="J6" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K6" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009678448419150776</v>
+        <v>0.009490604610421949</v>
       </c>
       <c r="M6" t="n">
-        <v>2.854456273233771</v>
+        <v>2.846349113927082</v>
       </c>
       <c r="N6" t="n">
-        <v>13.03015317272457</v>
+        <v>12.97979338364794</v>
       </c>
       <c r="O6" t="n">
-        <v>3.609730346261971</v>
+        <v>3.602748032217621</v>
       </c>
       <c r="P6" t="n">
-        <v>331.9515525253148</v>
+        <v>331.945082239857</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26563,28 +26667,28 @@
         <v>0.1982</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04296176397292852</v>
+        <v>0.04474421149714614</v>
       </c>
       <c r="J7" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K7" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007415320906989264</v>
+        <v>0.008092367400396205</v>
       </c>
       <c r="M7" t="n">
-        <v>3.082416747095079</v>
+        <v>3.077819218504038</v>
       </c>
       <c r="N7" t="n">
-        <v>14.58604003683263</v>
+        <v>14.54900167315832</v>
       </c>
       <c r="O7" t="n">
-        <v>3.819167453363708</v>
+        <v>3.814315360999706</v>
       </c>
       <c r="P7" t="n">
-        <v>325.5173259578459</v>
+        <v>325.4994031442865</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26641,28 +26745,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1011185251827646</v>
+        <v>0.1024270723472956</v>
       </c>
       <c r="J8" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K8" t="n">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04281169389759576</v>
+        <v>0.04418897766202501</v>
       </c>
       <c r="M8" t="n">
-        <v>3.100471273933103</v>
+        <v>3.093649763519408</v>
       </c>
       <c r="N8" t="n">
-        <v>13.55758466624281</v>
+        <v>13.51396120315357</v>
       </c>
       <c r="O8" t="n">
-        <v>3.682062555992607</v>
+        <v>3.676134002339084</v>
       </c>
       <c r="P8" t="n">
-        <v>324.2760342495561</v>
+        <v>324.2628938903608</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26719,28 +26823,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1786474929454092</v>
+        <v>0.1803290696730781</v>
       </c>
       <c r="J9" t="n">
+        <v>489</v>
+      </c>
+      <c r="K9" t="n">
         <v>487</v>
       </c>
-      <c r="K9" t="n">
-        <v>485</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.1356741406119889</v>
+        <v>0.1386771774711995</v>
       </c>
       <c r="M9" t="n">
-        <v>2.761734264178812</v>
+        <v>2.757869964717158</v>
       </c>
       <c r="N9" t="n">
-        <v>12.03704789622298</v>
+        <v>12.00775934191017</v>
       </c>
       <c r="O9" t="n">
-        <v>3.469444897418459</v>
+        <v>3.465221398685829</v>
       </c>
       <c r="P9" t="n">
-        <v>320.3136664039119</v>
+        <v>320.2967845325811</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26797,28 +26901,28 @@
         <v>0.1446</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05318669572191536</v>
+        <v>0.05822466615080719</v>
       </c>
       <c r="J10" t="n">
+        <v>489</v>
+      </c>
+      <c r="K10" t="n">
         <v>487</v>
       </c>
-      <c r="K10" t="n">
-        <v>485</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.009205846385148986</v>
+        <v>0.01099285405587325</v>
       </c>
       <c r="M10" t="n">
-        <v>3.470837870346188</v>
+        <v>3.481570748763829</v>
       </c>
       <c r="N10" t="n">
-        <v>18.02484095863647</v>
+        <v>18.13311898470402</v>
       </c>
       <c r="O10" t="n">
-        <v>4.245567212827571</v>
+        <v>4.258300011119933</v>
       </c>
       <c r="P10" t="n">
-        <v>318.7603849252974</v>
+        <v>318.7098052374205</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26875,28 +26979,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0667919059358954</v>
+        <v>0.070430365219236</v>
       </c>
       <c r="J11" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="K11" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L11" t="n">
-        <v>0.009701041417778722</v>
+        <v>0.01082658142052939</v>
       </c>
       <c r="M11" t="n">
-        <v>4.031517188393082</v>
+        <v>4.032010116348406</v>
       </c>
       <c r="N11" t="n">
-        <v>26.85797089247516</v>
+        <v>26.84195256718408</v>
       </c>
       <c r="O11" t="n">
-        <v>5.182467645096799</v>
+        <v>5.180921980418551</v>
       </c>
       <c r="P11" t="n">
-        <v>321.0180232242501</v>
+        <v>320.9814355221</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -26934,7 +27038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L488"/>
+  <dimension ref="A1:L490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57141,6 +57245,130 @@
         </is>
       </c>
     </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:21:11+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>-46.77733573215957,168.5303462976747</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>-46.7765191709856,168.52932294433285</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>-46.77665846765041,168.52842777283078</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>-46.77691008445051,168.52756682056165</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>-46.77723188076132,168.52677109381267</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>-46.777590987211745,168.5260296007051</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>-46.77799593888538,168.5253403313059</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>-46.77845547013222,168.52472991051386</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>-46.77896952634721,168.5242135590966</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>-46.77951238025093,168.52377958188939</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:21:16+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>-46.777351923990466,168.53034854255762</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>-46.77653040584505,168.52932499290873</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>-46.77666632748457,168.52842992545598</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>-46.77691803842578,168.5275705535349</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>-46.77723180223481,168.5267710302174</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>-46.77758796424273,168.5260263114263</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>-46.77799461719333,168.52533855854227</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>-46.77845604347201,168.524730917748</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>-46.77897585790392,168.52422722307747</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>-46.779513332925994,168.52378180027844</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0561/nzd0561.xlsx
+++ b/data/nzd0561/nzd0561.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L490"/>
+  <dimension ref="A1:L491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21002,6 +21002,48 @@
       <c r="L490" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:27:36+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>419.2</v>
+      </c>
+      <c r="C491" t="n">
+        <v>317.91</v>
+      </c>
+      <c r="D491" t="n">
+        <v>321.54</v>
+      </c>
+      <c r="E491" t="n">
+        <v>329.15</v>
+      </c>
+      <c r="F491" t="n">
+        <v>332.14</v>
+      </c>
+      <c r="G491" t="n">
+        <v>328.07</v>
+      </c>
+      <c r="H491" t="n">
+        <v>325.83</v>
+      </c>
+      <c r="I491" t="n">
+        <v>324.9</v>
+      </c>
+      <c r="J491" t="n">
+        <v>325.09</v>
+      </c>
+      <c r="K491" t="n">
+        <v>324.71</v>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21016,7 +21058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B509"/>
+  <dimension ref="A1:B510"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26109,6 +26151,16 @@
       </c>
       <c r="B509" t="n">
         <v>-0.74</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>-0.35</v>
       </c>
     </row>
   </sheetData>
@@ -26277,28 +26329,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.827623688354041</v>
+        <v>2.841416048435197</v>
       </c>
       <c r="J2" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K2" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2601738239994342</v>
+        <v>0.2624702127474606</v>
       </c>
       <c r="M2" t="n">
-        <v>31.03768108733989</v>
+        <v>31.03274016146778</v>
       </c>
       <c r="N2" t="n">
-        <v>1348.845397508032</v>
+        <v>1348.780728327068</v>
       </c>
       <c r="O2" t="n">
-        <v>36.72663063102893</v>
+        <v>36.72575020781834</v>
       </c>
       <c r="P2" t="n">
-        <v>307.8508476404879</v>
+        <v>307.7113556735882</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26355,28 +26407,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01031240922509876</v>
+        <v>0.01205713234472503</v>
       </c>
       <c r="J3" t="n">
+        <v>490</v>
+      </c>
+      <c r="K3" t="n">
         <v>489</v>
       </c>
-      <c r="K3" t="n">
-        <v>488</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0003315945115981433</v>
+        <v>0.0004540985414068777</v>
       </c>
       <c r="M3" t="n">
-        <v>3.376262953920083</v>
+        <v>3.379332994234045</v>
       </c>
       <c r="N3" t="n">
-        <v>19.02237855525441</v>
+        <v>19.02668409324146</v>
       </c>
       <c r="O3" t="n">
-        <v>4.361465184459737</v>
+        <v>4.361958745018281</v>
       </c>
       <c r="P3" t="n">
-        <v>313.0225311961323</v>
+        <v>313.0049167048355</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26433,28 +26485,28 @@
         <v>0.1302</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01917034177358425</v>
+        <v>-0.01711933582468093</v>
       </c>
       <c r="J4" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K4" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001208080441461368</v>
+        <v>0.0009644837013960128</v>
       </c>
       <c r="M4" t="n">
-        <v>3.379757255171731</v>
+        <v>3.384510082192022</v>
       </c>
       <c r="N4" t="n">
-        <v>17.99500662540152</v>
+        <v>18.01783758389781</v>
       </c>
       <c r="O4" t="n">
-        <v>4.242052171461534</v>
+        <v>4.244742345996729</v>
       </c>
       <c r="P4" t="n">
-        <v>316.6241629607206</v>
+        <v>316.6034421343807</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26511,28 +26563,28 @@
         <v>0.1707</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03565631537011406</v>
+        <v>-0.03439974897646858</v>
       </c>
       <c r="J5" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K5" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004740546922361477</v>
+        <v>0.004425937714566452</v>
       </c>
       <c r="M5" t="n">
-        <v>3.113916087638571</v>
+        <v>3.115029223983269</v>
       </c>
       <c r="N5" t="n">
-        <v>15.80861849670142</v>
+        <v>15.79871018451634</v>
       </c>
       <c r="O5" t="n">
-        <v>3.976005344149002</v>
+        <v>3.974759135408879</v>
       </c>
       <c r="P5" t="n">
-        <v>326.7792106850609</v>
+        <v>326.7665158930047</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26589,28 +26641,28 @@
         <v>0.1817</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0458242076109281</v>
+        <v>-0.04528888108561748</v>
       </c>
       <c r="J6" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K6" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009490604610421949</v>
+        <v>0.009307823942218407</v>
       </c>
       <c r="M6" t="n">
-        <v>2.846349113927082</v>
+        <v>2.843476938117375</v>
       </c>
       <c r="N6" t="n">
-        <v>12.97979338364794</v>
+        <v>12.95736119880176</v>
       </c>
       <c r="O6" t="n">
-        <v>3.602748032217621</v>
+        <v>3.599633481175793</v>
       </c>
       <c r="P6" t="n">
-        <v>331.945082239857</v>
+        <v>331.9396739630199</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26667,28 +26719,28 @@
         <v>0.1982</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04474421149714614</v>
+        <v>0.04526764909753616</v>
       </c>
       <c r="J7" t="n">
+        <v>490</v>
+      </c>
+      <c r="K7" t="n">
         <v>489</v>
       </c>
-      <c r="K7" t="n">
-        <v>488</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.008092367400396205</v>
+        <v>0.008313421369275154</v>
       </c>
       <c r="M7" t="n">
-        <v>3.077819218504038</v>
+        <v>3.073873925810803</v>
       </c>
       <c r="N7" t="n">
-        <v>14.54900167315832</v>
+        <v>14.52313598249345</v>
       </c>
       <c r="O7" t="n">
-        <v>3.814315360999706</v>
+        <v>3.810923245421435</v>
       </c>
       <c r="P7" t="n">
-        <v>325.4994031442865</v>
+        <v>325.4941149301218</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26745,28 +26797,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1024270723472956</v>
+        <v>0.1019945951589677</v>
       </c>
       <c r="J8" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K8" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04418897766202501</v>
+        <v>0.04399970825206179</v>
       </c>
       <c r="M8" t="n">
-        <v>3.093649763519408</v>
+        <v>3.090011707616202</v>
       </c>
       <c r="N8" t="n">
-        <v>13.51396120315357</v>
+        <v>13.48882575550719</v>
       </c>
       <c r="O8" t="n">
-        <v>3.676134002339084</v>
+        <v>3.672713677310987</v>
       </c>
       <c r="P8" t="n">
-        <v>324.2628938903608</v>
+        <v>324.2672575306448</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26823,28 +26875,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1803290696730781</v>
+        <v>0.1802625105465187</v>
       </c>
       <c r="J9" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K9" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1386771774711995</v>
+        <v>0.1390879630807063</v>
       </c>
       <c r="M9" t="n">
-        <v>2.757869964717158</v>
+        <v>2.752641132562802</v>
       </c>
       <c r="N9" t="n">
-        <v>12.00775934191017</v>
+        <v>11.98321631365154</v>
       </c>
       <c r="O9" t="n">
-        <v>3.465221398685829</v>
+        <v>3.461678251029628</v>
       </c>
       <c r="P9" t="n">
-        <v>320.2967845325811</v>
+        <v>320.2974558806469</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26901,28 +26953,28 @@
         <v>0.1446</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05822466615080719</v>
+        <v>0.0600549806402858</v>
       </c>
       <c r="J10" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K10" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01099285405587325</v>
+        <v>0.01170453197061216</v>
       </c>
       <c r="M10" t="n">
-        <v>3.481570748763829</v>
+        <v>3.483459152574162</v>
       </c>
       <c r="N10" t="n">
-        <v>18.13311898470402</v>
+        <v>18.14362870080967</v>
       </c>
       <c r="O10" t="n">
-        <v>4.258300011119933</v>
+        <v>4.259533859568401</v>
       </c>
       <c r="P10" t="n">
-        <v>318.7098052374205</v>
+        <v>318.69134378584</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -26979,28 +27031,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.070430365219236</v>
+        <v>0.07113549132943392</v>
       </c>
       <c r="J11" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="K11" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01082658142052939</v>
+        <v>0.01108494332810173</v>
       </c>
       <c r="M11" t="n">
-        <v>4.032010116348406</v>
+        <v>4.027084471540866</v>
       </c>
       <c r="N11" t="n">
-        <v>26.84195256718408</v>
+        <v>26.7942122404607</v>
       </c>
       <c r="O11" t="n">
-        <v>5.180921980418551</v>
+        <v>5.176312610387891</v>
       </c>
       <c r="P11" t="n">
-        <v>320.9814355221</v>
+        <v>320.9743118003551</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27038,7 +27090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L490"/>
+  <dimension ref="A1:L491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57369,6 +57421,68 @@
         </is>
       </c>
     </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:27:36+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>-46.77738403927929,168.5303529951184</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>-46.776560989629004,168.52933056959105</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>-46.7767136631145,168.5284428895925</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>-46.77694078850503,168.52758123064683</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>-46.77723627824543,168.5267746551488</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>-46.77758271003446,168.52602059434733</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>-46.777976443924885,168.52531418305136</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>-46.778442225980925,168.5247066434107</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>-46.778963898295544,168.5242014133386</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>-46.77949909042954,168.5237486353703</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0561/nzd0561.xlsx
+++ b/data/nzd0561/nzd0561.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L491"/>
+  <dimension ref="A1:L492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21044,6 +21044,48 @@
       <c r="L491" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:27:18+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>422.21</v>
+      </c>
+      <c r="C492" t="n">
+        <v>319.66</v>
+      </c>
+      <c r="D492" t="n">
+        <v>322.22</v>
+      </c>
+      <c r="E492" t="n">
+        <v>330.09</v>
+      </c>
+      <c r="F492" t="n">
+        <v>332.62</v>
+      </c>
+      <c r="G492" t="n">
+        <v>328.51</v>
+      </c>
+      <c r="H492" t="n">
+        <v>325.99</v>
+      </c>
+      <c r="I492" t="n">
+        <v>324.74</v>
+      </c>
+      <c r="J492" t="n">
+        <v>325.59</v>
+      </c>
+      <c r="K492" t="n">
+        <v>326.53</v>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21058,7 +21100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B510"/>
+  <dimension ref="A1:B511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26161,6 +26203,16 @@
       </c>
       <c r="B510" t="n">
         <v>-0.35</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>-0.63</v>
       </c>
     </row>
   </sheetData>
@@ -26329,28 +26381,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.841416048435197</v>
+        <v>2.856189908509609</v>
       </c>
       <c r="J2" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K2" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2624702127474606</v>
+        <v>0.2648503725353916</v>
       </c>
       <c r="M2" t="n">
-        <v>31.03274016146778</v>
+        <v>31.03151581908433</v>
       </c>
       <c r="N2" t="n">
-        <v>1348.780728327068</v>
+        <v>1349.115813515682</v>
       </c>
       <c r="O2" t="n">
-        <v>36.72575020781834</v>
+        <v>36.7303119169397</v>
       </c>
       <c r="P2" t="n">
-        <v>307.7113556735882</v>
+        <v>307.5614602057101</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26407,28 +26459,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01205713234472503</v>
+        <v>0.01445236396552856</v>
       </c>
       <c r="J3" t="n">
+        <v>491</v>
+      </c>
+      <c r="K3" t="n">
         <v>490</v>
       </c>
-      <c r="K3" t="n">
-        <v>489</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0004540985414068777</v>
+        <v>0.0006522590448342358</v>
       </c>
       <c r="M3" t="n">
-        <v>3.379332994234045</v>
+        <v>3.38611073962191</v>
       </c>
       <c r="N3" t="n">
-        <v>19.02668409324146</v>
+        <v>19.06916372407843</v>
       </c>
       <c r="O3" t="n">
-        <v>4.361958745018281</v>
+        <v>4.36682535992435</v>
       </c>
       <c r="P3" t="n">
-        <v>313.0049167048355</v>
+        <v>312.9806579159857</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26485,28 +26537,28 @@
         <v>0.1302</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01711933582468093</v>
+        <v>-0.01482391720980831</v>
       </c>
       <c r="J4" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K4" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0009644837013960128</v>
+        <v>0.0007234025234599262</v>
       </c>
       <c r="M4" t="n">
-        <v>3.384510082192022</v>
+        <v>3.390644459297176</v>
       </c>
       <c r="N4" t="n">
-        <v>18.01783758389781</v>
+        <v>18.05562652654922</v>
       </c>
       <c r="O4" t="n">
-        <v>4.244742345996729</v>
+        <v>4.249191279119971</v>
       </c>
       <c r="P4" t="n">
-        <v>316.6034421343807</v>
+        <v>316.5801786217556</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26563,28 +26615,28 @@
         <v>0.1707</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03439974897646858</v>
+        <v>-0.03279486681751764</v>
       </c>
       <c r="J5" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K5" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004425937714566452</v>
+        <v>0.004031810379561462</v>
       </c>
       <c r="M5" t="n">
-        <v>3.115029223983269</v>
+        <v>3.118195961872802</v>
       </c>
       <c r="N5" t="n">
-        <v>15.79871018451634</v>
+        <v>15.80294455074773</v>
       </c>
       <c r="O5" t="n">
-        <v>3.974759135408879</v>
+        <v>3.975291756682486</v>
       </c>
       <c r="P5" t="n">
-        <v>326.7665158930047</v>
+        <v>326.7502508003874</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26641,28 +26693,28 @@
         <v>0.1817</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04528888108561748</v>
+        <v>-0.04457806336682824</v>
       </c>
       <c r="J6" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K6" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009307823942218407</v>
+        <v>0.009053211247848192</v>
       </c>
       <c r="M6" t="n">
-        <v>2.843476938117375</v>
+        <v>2.841554423026895</v>
       </c>
       <c r="N6" t="n">
-        <v>12.95736119880176</v>
+        <v>12.93811416072979</v>
       </c>
       <c r="O6" t="n">
-        <v>3.599633481175793</v>
+        <v>3.596959015714495</v>
       </c>
       <c r="P6" t="n">
-        <v>331.9396739630199</v>
+        <v>331.9324699973171</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26719,28 +26771,28 @@
         <v>0.1982</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04526764909753616</v>
+        <v>0.04595374507782349</v>
       </c>
       <c r="J7" t="n">
+        <v>491</v>
+      </c>
+      <c r="K7" t="n">
         <v>490</v>
       </c>
-      <c r="K7" t="n">
-        <v>489</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.008313421369275154</v>
+        <v>0.008596932107188926</v>
       </c>
       <c r="M7" t="n">
-        <v>3.073873925810803</v>
+        <v>3.070663894965743</v>
       </c>
       <c r="N7" t="n">
-        <v>14.52313598249345</v>
+        <v>14.50016485826231</v>
       </c>
       <c r="O7" t="n">
-        <v>3.810923245421435</v>
+        <v>3.807908199820777</v>
       </c>
       <c r="P7" t="n">
-        <v>325.4941149301218</v>
+        <v>325.4871613831168</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26797,28 +26849,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1019945951589677</v>
+        <v>0.1016228745328936</v>
       </c>
       <c r="J8" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K8" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04399970825206179</v>
+        <v>0.04386264394025785</v>
       </c>
       <c r="M8" t="n">
-        <v>3.090011707616202</v>
+        <v>3.085994055988098</v>
       </c>
       <c r="N8" t="n">
-        <v>13.48882575550719</v>
+        <v>13.46309824349918</v>
       </c>
       <c r="O8" t="n">
-        <v>3.672713677310987</v>
+        <v>3.669209484820836</v>
       </c>
       <c r="P8" t="n">
-        <v>324.2672575306448</v>
+        <v>324.2710201747138</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26875,28 +26927,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1802625105465187</v>
+        <v>0.1801297101548448</v>
       </c>
       <c r="J9" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K9" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1390879630807063</v>
+        <v>0.1394114274429546</v>
       </c>
       <c r="M9" t="n">
-        <v>2.752641132562802</v>
+        <v>2.747849016254263</v>
       </c>
       <c r="N9" t="n">
-        <v>11.98321631365154</v>
+        <v>11.95896132662532</v>
       </c>
       <c r="O9" t="n">
-        <v>3.461678251029628</v>
+        <v>3.458173119817069</v>
       </c>
       <c r="P9" t="n">
-        <v>320.2974558806469</v>
+        <v>320.2987996423566</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -26953,28 +27005,28 @@
         <v>0.1446</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0600549806402858</v>
+        <v>0.06205875146652991</v>
       </c>
       <c r="J10" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K10" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01170453197061216</v>
+        <v>0.01250163404370919</v>
       </c>
       <c r="M10" t="n">
-        <v>3.483459152574162</v>
+        <v>3.486214097981397</v>
       </c>
       <c r="N10" t="n">
-        <v>18.14362870080967</v>
+        <v>18.16357083223142</v>
       </c>
       <c r="O10" t="n">
-        <v>4.259533859568401</v>
+        <v>4.261874098589893</v>
       </c>
       <c r="P10" t="n">
-        <v>318.69134378584</v>
+        <v>318.67106831468</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27031,28 +27083,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07113549132943392</v>
+        <v>0.07252160475080639</v>
       </c>
       <c r="J11" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="K11" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01108494332810173</v>
+        <v>0.01155241724272382</v>
       </c>
       <c r="M11" t="n">
-        <v>4.027084471540866</v>
+        <v>4.025333570234235</v>
       </c>
       <c r="N11" t="n">
-        <v>26.7942122404607</v>
+        <v>26.76680239817549</v>
       </c>
       <c r="O11" t="n">
-        <v>5.176312610387891</v>
+        <v>5.173664310541948</v>
       </c>
       <c r="P11" t="n">
-        <v>320.9743118003551</v>
+        <v>320.9602638759944</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27090,7 +27142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L491"/>
+  <dimension ref="A1:L492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57483,6 +57535,68 @@
         </is>
       </c>
     </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:27:18+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>-46.77741096602554,168.53035672832698</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>-46.776576593600346,168.52933341483907</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>-46.7767196683809,168.52844453429776</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>-46.776948828006546,168.5275850037636</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>-46.77724004751743,168.52677770772308</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>-46.77758587695453,168.52602404025782</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>-46.77797750127881,168.52531560126133</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>-46.77844130863694,168.52470503183687</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>-46.77896641081877,168.52420683555167</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>-46.779507759776294,168.52376882270357</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0561/nzd0561.xlsx
+++ b/data/nzd0561/nzd0561.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L492"/>
+  <dimension ref="A1:L493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21086,6 +21086,48 @@
       <c r="L492" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:27:17+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>423.41</v>
+      </c>
+      <c r="C493" t="n">
+        <v>321.14</v>
+      </c>
+      <c r="D493" t="n">
+        <v>323.14</v>
+      </c>
+      <c r="E493" t="n">
+        <v>330.37</v>
+      </c>
+      <c r="F493" t="n">
+        <v>332.52</v>
+      </c>
+      <c r="G493" t="n">
+        <v>327.35</v>
+      </c>
+      <c r="H493" t="n">
+        <v>325.1</v>
+      </c>
+      <c r="I493" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="J493" t="n">
+        <v>324.31</v>
+      </c>
+      <c r="K493" t="n">
+        <v>325.88</v>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21100,7 +21142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B511"/>
+  <dimension ref="A1:B512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26213,6 +26255,16 @@
       </c>
       <c r="B511" t="n">
         <v>-0.63</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>0.76</v>
       </c>
     </row>
   </sheetData>
@@ -26381,28 +26433,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.856189908509609</v>
+        <v>2.871251593178367</v>
       </c>
       <c r="J2" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K2" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2648503725353916</v>
+        <v>0.2672591433390211</v>
       </c>
       <c r="M2" t="n">
-        <v>31.03151581908433</v>
+        <v>31.03117408223676</v>
       </c>
       <c r="N2" t="n">
-        <v>1349.115813515682</v>
+        <v>1349.573098792878</v>
       </c>
       <c r="O2" t="n">
-        <v>36.7303119169397</v>
+        <v>36.73653629280907</v>
       </c>
       <c r="P2" t="n">
-        <v>307.5614602057101</v>
+        <v>307.4081610443693</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26459,28 +26511,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01445236396552856</v>
+        <v>0.01739156728023627</v>
       </c>
       <c r="J3" t="n">
+        <v>492</v>
+      </c>
+      <c r="K3" t="n">
         <v>491</v>
       </c>
-      <c r="K3" t="n">
-        <v>490</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.0006522590448342358</v>
+        <v>0.0009421958554408638</v>
       </c>
       <c r="M3" t="n">
-        <v>3.38611073962191</v>
+        <v>3.395914164560003</v>
       </c>
       <c r="N3" t="n">
-        <v>19.06916372407843</v>
+        <v>19.15258851146159</v>
       </c>
       <c r="O3" t="n">
-        <v>4.36682535992435</v>
+        <v>4.376367044874274</v>
       </c>
       <c r="P3" t="n">
-        <v>312.9806579159857</v>
+        <v>312.9507960354783</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26537,28 +26589,28 @@
         <v>0.1302</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01482391720980831</v>
+        <v>-0.01219155949000158</v>
       </c>
       <c r="J4" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K4" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007234025234599262</v>
+        <v>0.0004888248546772722</v>
       </c>
       <c r="M4" t="n">
-        <v>3.390644459297176</v>
+        <v>3.399044972758405</v>
       </c>
       <c r="N4" t="n">
-        <v>18.05562652654922</v>
+        <v>18.11674756965276</v>
       </c>
       <c r="O4" t="n">
-        <v>4.249191279119971</v>
+        <v>4.256377282343843</v>
       </c>
       <c r="P4" t="n">
-        <v>316.5801786217556</v>
+        <v>316.553416562997</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26615,28 +26667,28 @@
         <v>0.1707</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03279486681751764</v>
+        <v>-0.03109639357965043</v>
       </c>
       <c r="J5" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K5" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004031810379561462</v>
+        <v>0.00363239079351052</v>
       </c>
       <c r="M5" t="n">
-        <v>3.118195961872802</v>
+        <v>3.122084400161846</v>
       </c>
       <c r="N5" t="n">
-        <v>15.80294455074773</v>
+        <v>15.81154897770423</v>
       </c>
       <c r="O5" t="n">
-        <v>3.975291756682486</v>
+        <v>3.976373847829732</v>
       </c>
       <c r="P5" t="n">
-        <v>326.7502508003874</v>
+        <v>326.73298314704</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26693,28 +26745,28 @@
         <v>0.1817</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04457806336682824</v>
+        <v>-0.04390671850855845</v>
       </c>
       <c r="J6" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K6" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L6" t="n">
-        <v>0.009053211247848192</v>
+        <v>0.008817422150908305</v>
       </c>
       <c r="M6" t="n">
-        <v>2.841554423026895</v>
+        <v>2.839403966430287</v>
       </c>
       <c r="N6" t="n">
-        <v>12.93811416072979</v>
+        <v>12.91817966659575</v>
       </c>
       <c r="O6" t="n">
-        <v>3.596959015714495</v>
+        <v>3.594186927052591</v>
       </c>
       <c r="P6" t="n">
-        <v>331.9324699973171</v>
+        <v>331.9256447203385</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26771,28 +26823,28 @@
         <v>0.1982</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04595374507782349</v>
+        <v>0.04619542675286353</v>
       </c>
       <c r="J7" t="n">
+        <v>492</v>
+      </c>
+      <c r="K7" t="n">
         <v>491</v>
       </c>
-      <c r="K7" t="n">
-        <v>490</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.008596932107188926</v>
+        <v>0.008722641334725778</v>
       </c>
       <c r="M7" t="n">
-        <v>3.070663894965743</v>
+        <v>3.065479630315445</v>
       </c>
       <c r="N7" t="n">
-        <v>14.50016485826231</v>
+        <v>14.47145916586033</v>
       </c>
       <c r="O7" t="n">
-        <v>3.807908199820777</v>
+        <v>3.804137111863916</v>
       </c>
       <c r="P7" t="n">
-        <v>325.4871613831168</v>
+        <v>325.4847042393999</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26849,28 +26901,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1016228745328936</v>
+        <v>0.1009143046797136</v>
       </c>
       <c r="J8" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K8" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04386264394025785</v>
+        <v>0.04343164168675173</v>
       </c>
       <c r="M8" t="n">
-        <v>3.085994055988098</v>
+        <v>3.084074572013821</v>
       </c>
       <c r="N8" t="n">
-        <v>13.46309824349918</v>
+        <v>13.44265868107284</v>
       </c>
       <c r="O8" t="n">
-        <v>3.669209484820836</v>
+        <v>3.666423145392911</v>
       </c>
       <c r="P8" t="n">
-        <v>324.2710201747138</v>
+        <v>324.2782152876933</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26927,28 +26979,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1801297101548448</v>
+        <v>0.1795257805747092</v>
       </c>
       <c r="J9" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K9" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1394114274429546</v>
+        <v>0.1390588771197879</v>
       </c>
       <c r="M9" t="n">
-        <v>2.747849016254263</v>
+        <v>2.746020252274224</v>
       </c>
       <c r="N9" t="n">
-        <v>11.95896132662532</v>
+        <v>11.939729968535</v>
       </c>
       <c r="O9" t="n">
-        <v>3.458173119817069</v>
+        <v>3.455391434922388</v>
       </c>
       <c r="P9" t="n">
-        <v>320.2987996423566</v>
+        <v>320.3049299157788</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27005,28 +27057,28 @@
         <v>0.1446</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06205875146652991</v>
+        <v>0.06356624272940278</v>
       </c>
       <c r="J10" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K10" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01250163404370919</v>
+        <v>0.01313980819620553</v>
       </c>
       <c r="M10" t="n">
-        <v>3.486214097981397</v>
+        <v>3.486503191437963</v>
       </c>
       <c r="N10" t="n">
-        <v>18.16357083223142</v>
+        <v>18.15874424497111</v>
       </c>
       <c r="O10" t="n">
-        <v>4.261874098589893</v>
+        <v>4.261307809226073</v>
       </c>
       <c r="P10" t="n">
-        <v>318.67106831468</v>
+        <v>318.6557663094015</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27083,28 +27135,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07252160475080639</v>
+        <v>0.07365151090386354</v>
       </c>
       <c r="J11" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K11" t="n">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01155241724272382</v>
+        <v>0.01195260678728971</v>
       </c>
       <c r="M11" t="n">
-        <v>4.025333570234235</v>
+        <v>4.022411620858957</v>
       </c>
       <c r="N11" t="n">
-        <v>26.76680239817549</v>
+        <v>26.7304210444541</v>
       </c>
       <c r="O11" t="n">
-        <v>5.173664310541948</v>
+        <v>5.170147100852557</v>
       </c>
       <c r="P11" t="n">
-        <v>320.9602638759944</v>
+        <v>320.9487766018172</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27142,7 +27194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L492"/>
+  <dimension ref="A1:L493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57597,6 +57649,68 @@
         </is>
       </c>
     </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-27 22:27:17+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>-46.77742170094095,168.53035821665011</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>-46.776589790101795,168.52933582110703</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>-46.776727793153086,168.52844675948782</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>-46.776951222751656,168.5275861276709</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>-46.777239262252436,168.52677707177008</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>-46.777577527801405,168.52601495558562</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>-46.77797161974739,168.52530771246927</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>-46.778434199220435,168.52469254214168</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>-46.778959978758834,168.52419295468724</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>-46.77950466358141,168.52376161294092</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0561/nzd0561.xlsx
+++ b/data/nzd0561/nzd0561.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L493"/>
+  <dimension ref="A1:L496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21128,6 +21128,132 @@
       <c r="L493" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:41+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>427.87</v>
+      </c>
+      <c r="C494" t="n">
+        <v>320.1</v>
+      </c>
+      <c r="D494" t="n">
+        <v>324.25</v>
+      </c>
+      <c r="E494" t="n">
+        <v>331.28</v>
+      </c>
+      <c r="F494" t="n">
+        <v>333.6</v>
+      </c>
+      <c r="G494" t="n">
+        <v>328.75</v>
+      </c>
+      <c r="H494" t="n">
+        <v>326.26</v>
+      </c>
+      <c r="I494" t="n">
+        <v>325.63</v>
+      </c>
+      <c r="J494" t="n">
+        <v>326.86</v>
+      </c>
+      <c r="K494" t="n">
+        <v>330.43</v>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>423.8</v>
+      </c>
+      <c r="C495" t="n">
+        <v>319.39</v>
+      </c>
+      <c r="D495" t="n">
+        <v>323.83</v>
+      </c>
+      <c r="E495" t="n">
+        <v>330.58</v>
+      </c>
+      <c r="F495" t="n">
+        <v>333.58</v>
+      </c>
+      <c r="G495" t="n">
+        <v>329.09</v>
+      </c>
+      <c r="H495" t="n">
+        <v>326.46</v>
+      </c>
+      <c r="I495" t="n">
+        <v>326.19</v>
+      </c>
+      <c r="J495" t="n">
+        <v>326.73</v>
+      </c>
+      <c r="K495" t="n">
+        <v>331.16</v>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>423.8</v>
+      </c>
+      <c r="C496" t="n">
+        <v>318.1</v>
+      </c>
+      <c r="D496" t="n">
+        <v>320.99</v>
+      </c>
+      <c r="E496" t="n">
+        <v>329.42</v>
+      </c>
+      <c r="F496" t="n">
+        <v>334.08</v>
+      </c>
+      <c r="G496" t="n">
+        <v>330.49</v>
+      </c>
+      <c r="H496" t="n">
+        <v>328.1</v>
+      </c>
+      <c r="I496" t="n">
+        <v>327.6</v>
+      </c>
+      <c r="J496" t="n">
+        <v>327.77</v>
+      </c>
+      <c r="K496" t="n">
+        <v>330.47</v>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -21142,7 +21268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B512"/>
+  <dimension ref="A1:B515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26265,6 +26391,36 @@
       </c>
       <c r="B512" t="n">
         <v>0.76</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
@@ -26433,28 +26589,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.871251593178367</v>
+        <v>2.917366307267924</v>
       </c>
       <c r="J2" t="n">
+        <v>495</v>
+      </c>
+      <c r="K2" t="n">
         <v>492</v>
       </c>
-      <c r="K2" t="n">
-        <v>489</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.2672591433390211</v>
+        <v>0.2745808144712641</v>
       </c>
       <c r="M2" t="n">
-        <v>31.03117408223676</v>
+        <v>31.03445035931838</v>
       </c>
       <c r="N2" t="n">
-        <v>1349.573098792878</v>
+        <v>1351.394870017885</v>
       </c>
       <c r="O2" t="n">
-        <v>36.73653629280907</v>
+        <v>36.76132301778439</v>
       </c>
       <c r="P2" t="n">
-        <v>307.4081610443693</v>
+        <v>306.936178241041</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26511,28 +26667,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01739156728023627</v>
+        <v>0.02389683676615797</v>
       </c>
       <c r="J3" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K3" t="n">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009421958554408638</v>
+        <v>0.001781049095182952</v>
       </c>
       <c r="M3" t="n">
-        <v>3.395914164560003</v>
+        <v>3.41192245709461</v>
       </c>
       <c r="N3" t="n">
-        <v>19.15258851146159</v>
+        <v>19.23967772503648</v>
       </c>
       <c r="O3" t="n">
-        <v>4.376367044874274</v>
+        <v>4.386305703554698</v>
       </c>
       <c r="P3" t="n">
-        <v>312.9507960354783</v>
+        <v>312.8843398230508</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26589,28 +26745,28 @@
         <v>0.1302</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01219155949000158</v>
+        <v>-0.004543713491073262</v>
       </c>
       <c r="J4" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K4" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0004888248546772722</v>
+        <v>6.771385958692644e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>3.399044972758405</v>
+        <v>3.422435959209879</v>
       </c>
       <c r="N4" t="n">
-        <v>18.11674756965276</v>
+        <v>18.29439830893055</v>
       </c>
       <c r="O4" t="n">
-        <v>4.256377282343843</v>
+        <v>4.277195145060668</v>
       </c>
       <c r="P4" t="n">
-        <v>316.553416562997</v>
+        <v>316.4752395152012</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26667,28 +26823,28 @@
         <v>0.1707</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03109639357965043</v>
+        <v>-0.02600159921861779</v>
       </c>
       <c r="J5" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K5" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00363239079351052</v>
+        <v>0.002554489813110017</v>
       </c>
       <c r="M5" t="n">
-        <v>3.122084400161846</v>
+        <v>3.134060263475371</v>
       </c>
       <c r="N5" t="n">
-        <v>15.81154897770423</v>
+        <v>15.84121013478089</v>
       </c>
       <c r="O5" t="n">
-        <v>3.976373847829732</v>
+        <v>3.980101774424982</v>
       </c>
       <c r="P5" t="n">
-        <v>326.73298314704</v>
+        <v>326.6809037226632</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26745,28 +26901,28 @@
         <v>0.1817</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04390671850855845</v>
+        <v>-0.04052791780485417</v>
       </c>
       <c r="J6" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K6" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008817422150908305</v>
+        <v>0.007586188164398044</v>
       </c>
       <c r="M6" t="n">
-        <v>2.839403966430287</v>
+        <v>2.8402157262943</v>
       </c>
       <c r="N6" t="n">
-        <v>12.91817966659575</v>
+        <v>12.89380218786079</v>
       </c>
       <c r="O6" t="n">
-        <v>3.594186927052591</v>
+        <v>3.590794088758194</v>
       </c>
       <c r="P6" t="n">
-        <v>331.9256447203385</v>
+        <v>331.8911004938678</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26823,28 +26979,28 @@
         <v>0.1982</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04619542675286353</v>
+        <v>0.04926035777738088</v>
       </c>
       <c r="J7" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K7" t="n">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008722641334725778</v>
+        <v>0.009999109331565448</v>
       </c>
       <c r="M7" t="n">
-        <v>3.065479630315445</v>
+        <v>3.06033709075109</v>
       </c>
       <c r="N7" t="n">
-        <v>14.47145916586033</v>
+        <v>14.43117708262102</v>
       </c>
       <c r="O7" t="n">
-        <v>3.804137111863916</v>
+        <v>3.798838912433775</v>
       </c>
       <c r="P7" t="n">
-        <v>325.4847042393999</v>
+        <v>325.4533630328972</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -26901,28 +27057,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1009143046797136</v>
+        <v>0.1008712744151016</v>
       </c>
       <c r="J8" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K8" t="n">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04343164168675173</v>
+        <v>0.04391189270749685</v>
       </c>
       <c r="M8" t="n">
-        <v>3.084074572013821</v>
+        <v>3.070050793533412</v>
       </c>
       <c r="N8" t="n">
-        <v>13.44265868107284</v>
+        <v>13.36465091167288</v>
       </c>
       <c r="O8" t="n">
-        <v>3.666423145392911</v>
+        <v>3.655769537549225</v>
       </c>
       <c r="P8" t="n">
-        <v>324.2782152876933</v>
+        <v>324.2786490601458</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -26979,28 +27135,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1795257805747092</v>
+        <v>0.1810648225991105</v>
       </c>
       <c r="J9" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K9" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1390588771197879</v>
+        <v>0.1425020503998924</v>
       </c>
       <c r="M9" t="n">
-        <v>2.746020252274224</v>
+        <v>2.736158842684341</v>
       </c>
       <c r="N9" t="n">
-        <v>11.939729968535</v>
+        <v>11.88241134938411</v>
       </c>
       <c r="O9" t="n">
-        <v>3.455391434922388</v>
+        <v>3.447087371881385</v>
       </c>
       <c r="P9" t="n">
-        <v>320.3049299157788</v>
+        <v>320.289212813206</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27057,28 +27213,28 @@
         <v>0.1446</v>
       </c>
       <c r="I10" t="n">
-        <v>0.06356624272940278</v>
+        <v>0.07117692168203517</v>
       </c>
       <c r="J10" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K10" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01313980819620553</v>
+        <v>0.01638090921334245</v>
       </c>
       <c r="M10" t="n">
-        <v>3.486503191437963</v>
+        <v>3.502746139822345</v>
       </c>
       <c r="N10" t="n">
-        <v>18.15874424497111</v>
+        <v>18.32279773655694</v>
       </c>
       <c r="O10" t="n">
-        <v>4.261307809226073</v>
+        <v>4.280513723439856</v>
       </c>
       <c r="P10" t="n">
-        <v>318.6557663094015</v>
+        <v>318.5780757392151</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27135,28 +27291,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.07365151090386354</v>
+        <v>0.08239367627744715</v>
       </c>
       <c r="J11" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K11" t="n">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01195260678728971</v>
+        <v>0.01490281432071716</v>
       </c>
       <c r="M11" t="n">
-        <v>4.022411620858957</v>
+        <v>4.038681742033133</v>
       </c>
       <c r="N11" t="n">
-        <v>26.7304210444541</v>
+        <v>26.92785623731752</v>
       </c>
       <c r="O11" t="n">
-        <v>5.170147100852557</v>
+        <v>5.189205742434725</v>
       </c>
       <c r="P11" t="n">
-        <v>320.9487766018172</v>
+        <v>320.8593998969345</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27194,7 +27350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L493"/>
+  <dimension ref="A1:L496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57711,6 +57867,192 @@
         </is>
       </c>
     </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:41+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>-46.77746159904317,168.5303637482549</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>-46.77658051688456,168.52933413021594</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>-46.77673759586732,168.52844944422873</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>-46.77695900567322,168.52758978037033</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>-46.777247743114245,168.52678394006352</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>-46.77758760436546,168.52602591984552</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>-46.77797928556353,168.5253179944907</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>-46.77844641136254,168.52471399621695</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>-46.77897279262667,168.52422060797522</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>-46.77952633693658,168.5238120812972</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>-46.77742518978845,168.53035870035524</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>-46.77657418613049,168.52933297585787</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>-46.77673388673221,168.5284484283807</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>-46.77695301881049,168.52758697060145</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>-46.77724758606126,168.52678381287288</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>-46.777590051530865,168.52602858259496</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>-46.77798060725589,168.5253197672533</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>-46.778449622065956,168.52471963672662</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>-46.7789721393708,168.5242191981994</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>-46.7795298141982,168.52382017842197</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>-46.77742518978845,168.53035870035524</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>-46.77656268377448,168.52933087850363</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>-46.77670880591371,168.52844155931635</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>-46.77694309772355,168.5275823144143</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>-46.777251512386044,168.52678699263907</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>-46.777600128093766,168.52603954685986</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>-46.777991445132265,168.52533430390997</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>-46.77845770615734,168.5247338387272</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>-46.77897736541719,168.52423047640673</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>-46.779526527471475,168.52381252497526</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0561/nzd0561.xlsx
+++ b/data/nzd0561/nzd0561.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L496"/>
+  <dimension ref="A1:L499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21254,6 +21254,132 @@
       <c r="L496" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>422.68</v>
+      </c>
+      <c r="C497" t="n">
+        <v>315.15</v>
+      </c>
+      <c r="D497" t="n">
+        <v>317.97</v>
+      </c>
+      <c r="E497" t="n">
+        <v>326.69</v>
+      </c>
+      <c r="F497" t="n">
+        <v>331.33</v>
+      </c>
+      <c r="G497" t="n">
+        <v>328.09</v>
+      </c>
+      <c r="H497" t="n">
+        <v>326.61</v>
+      </c>
+      <c r="I497" t="n">
+        <v>325.8</v>
+      </c>
+      <c r="J497" t="n">
+        <v>325.89</v>
+      </c>
+      <c r="K497" t="n">
+        <v>328.78</v>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>415</v>
+      </c>
+      <c r="C498" t="n">
+        <v>312.64</v>
+      </c>
+      <c r="D498" t="n">
+        <v>314.22</v>
+      </c>
+      <c r="E498" t="n">
+        <v>324.89</v>
+      </c>
+      <c r="F498" t="n">
+        <v>330.14</v>
+      </c>
+      <c r="G498" t="n">
+        <v>326.91</v>
+      </c>
+      <c r="H498" t="n">
+        <v>326.39</v>
+      </c>
+      <c r="I498" t="n">
+        <v>325.45</v>
+      </c>
+      <c r="J498" t="n">
+        <v>325.04</v>
+      </c>
+      <c r="K498" t="n">
+        <v>325.75</v>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>415</v>
+      </c>
+      <c r="C499" t="n">
+        <v>311.93</v>
+      </c>
+      <c r="D499" t="n">
+        <v>313.35</v>
+      </c>
+      <c r="E499" t="n">
+        <v>324.12</v>
+      </c>
+      <c r="F499" t="n">
+        <v>329.01</v>
+      </c>
+      <c r="G499" t="n">
+        <v>325.42</v>
+      </c>
+      <c r="H499" t="n">
+        <v>324.62</v>
+      </c>
+      <c r="I499" t="n">
+        <v>323.58</v>
+      </c>
+      <c r="J499" t="n">
+        <v>322.62</v>
+      </c>
+      <c r="K499" t="n">
+        <v>323.65</v>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21268,7 +21394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B515"/>
+  <dimension ref="A1:B518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26421,6 +26547,36 @@
       </c>
       <c r="B515" t="n">
         <v>0.15</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>0.76</v>
       </c>
     </row>
   </sheetData>
@@ -26589,28 +26745,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>2.917366307267924</v>
+        <v>2.95338297717159</v>
       </c>
       <c r="J2" t="n">
+        <v>498</v>
+      </c>
+      <c r="K2" t="n">
         <v>495</v>
       </c>
-      <c r="K2" t="n">
-        <v>492</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.2745808144712641</v>
+        <v>0.2810944986350696</v>
       </c>
       <c r="M2" t="n">
-        <v>31.03445035931838</v>
+        <v>30.99424689081135</v>
       </c>
       <c r="N2" t="n">
-        <v>1351.394870017885</v>
+        <v>1349.482621915649</v>
       </c>
       <c r="O2" t="n">
-        <v>36.76132301778439</v>
+        <v>36.73530484310221</v>
       </c>
       <c r="P2" t="n">
-        <v>306.936178241041</v>
+        <v>306.565769157761</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -26667,28 +26823,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02389683676615797</v>
+        <v>0.02357597976662444</v>
       </c>
       <c r="J3" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="K3" t="n">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001781049095182952</v>
+        <v>0.001754491339299613</v>
       </c>
       <c r="M3" t="n">
-        <v>3.41192245709461</v>
+        <v>3.399486195258126</v>
       </c>
       <c r="N3" t="n">
-        <v>19.23967772503648</v>
+        <v>19.13551445292137</v>
       </c>
       <c r="O3" t="n">
-        <v>4.386305703554698</v>
+        <v>4.374415898485347</v>
       </c>
       <c r="P3" t="n">
-        <v>312.8843398230508</v>
+        <v>312.8876465508261</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -26745,28 +26901,28 @@
         <v>0.1302</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.004543713491073262</v>
+        <v>-0.005857603149579487</v>
       </c>
       <c r="J4" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="K4" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="L4" t="n">
-        <v>6.771385958692644e-05</v>
+        <v>0.0001137583765541406</v>
       </c>
       <c r="M4" t="n">
-        <v>3.422435959209879</v>
+        <v>3.414855490669918</v>
       </c>
       <c r="N4" t="n">
-        <v>18.29439830893055</v>
+        <v>18.21659487929854</v>
       </c>
       <c r="O4" t="n">
-        <v>4.277195145060668</v>
+        <v>4.268090308240741</v>
       </c>
       <c r="P4" t="n">
-        <v>316.4752395152012</v>
+        <v>316.4887550171956</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -26823,28 +26979,28 @@
         <v>0.1707</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02600159921861779</v>
+        <v>-0.02683641634864</v>
       </c>
       <c r="J5" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="K5" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002554489813110017</v>
+        <v>0.002753364790884505</v>
       </c>
       <c r="M5" t="n">
-        <v>3.134060263475371</v>
+        <v>3.121891254907366</v>
       </c>
       <c r="N5" t="n">
-        <v>15.84121013478089</v>
+        <v>15.75607249192746</v>
       </c>
       <c r="O5" t="n">
-        <v>3.980101774424982</v>
+        <v>3.969391954938119</v>
       </c>
       <c r="P5" t="n">
-        <v>326.6809037226632</v>
+        <v>326.6894897392792</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -26901,28 +27057,28 @@
         <v>0.1817</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.04052791780485417</v>
+        <v>-0.04124648870030487</v>
       </c>
       <c r="J6" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="K6" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007586188164398044</v>
+        <v>0.007949578484624631</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8402157262943</v>
+        <v>2.829118986861949</v>
       </c>
       <c r="N6" t="n">
-        <v>12.89380218786079</v>
+        <v>12.82400603924217</v>
       </c>
       <c r="O6" t="n">
-        <v>3.590794088758194</v>
+        <v>3.581062138422367</v>
       </c>
       <c r="P6" t="n">
-        <v>331.8911004938678</v>
+        <v>331.8984913760648</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -26979,28 +27135,28 @@
         <v>0.1982</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04926035777738088</v>
+        <v>0.04929361440389655</v>
       </c>
       <c r="J7" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="K7" t="n">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009999109331565448</v>
+        <v>0.01013319647718192</v>
       </c>
       <c r="M7" t="n">
-        <v>3.06033709075109</v>
+        <v>3.047468111172222</v>
       </c>
       <c r="N7" t="n">
-        <v>14.43117708262102</v>
+        <v>14.35126802648807</v>
       </c>
       <c r="O7" t="n">
-        <v>3.798838912433775</v>
+        <v>3.788306749259894</v>
       </c>
       <c r="P7" t="n">
-        <v>325.4533630328972</v>
+        <v>325.4530319041745</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27057,28 +27213,28 @@
         <v>0.2</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1008712744151016</v>
+        <v>0.09962833208667907</v>
       </c>
       <c r="J8" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="K8" t="n">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04391189270749685</v>
+        <v>0.04336364943832272</v>
       </c>
       <c r="M8" t="n">
-        <v>3.070050793533412</v>
+        <v>3.058980834195813</v>
       </c>
       <c r="N8" t="n">
-        <v>13.36465091167288</v>
+        <v>13.29571963616734</v>
       </c>
       <c r="O8" t="n">
-        <v>3.655769537549225</v>
+        <v>3.646329611563845</v>
       </c>
       <c r="P8" t="n">
-        <v>324.2786490601458</v>
+        <v>324.2914118920979</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27135,28 +27291,28 @@
         <v>0.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1810648225991105</v>
+        <v>0.180829272310661</v>
       </c>
       <c r="J9" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="K9" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1425020503998924</v>
+        <v>0.1436659328567984</v>
       </c>
       <c r="M9" t="n">
-        <v>2.736158842684341</v>
+        <v>2.724913803016627</v>
       </c>
       <c r="N9" t="n">
-        <v>11.88241134938411</v>
+        <v>11.81654992810905</v>
       </c>
       <c r="O9" t="n">
-        <v>3.447087371881385</v>
+        <v>3.437520898570516</v>
       </c>
       <c r="P9" t="n">
-        <v>320.289212813206</v>
+        <v>320.2916377380301</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27213,28 +27369,28 @@
         <v>0.1446</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07117692168203517</v>
+        <v>0.07566392451935965</v>
       </c>
       <c r="J10" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="K10" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01638090921334245</v>
+        <v>0.01859369110062181</v>
       </c>
       <c r="M10" t="n">
-        <v>3.502746139822345</v>
+        <v>3.503916750427975</v>
       </c>
       <c r="N10" t="n">
-        <v>18.32279773655694</v>
+        <v>18.3199701285881</v>
       </c>
       <c r="O10" t="n">
-        <v>4.280513723439856</v>
+        <v>4.280183422306584</v>
       </c>
       <c r="P10" t="n">
-        <v>318.5780757392151</v>
+        <v>318.5320635794697</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -27291,28 +27447,28 @@
         <v>0.08359999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.08239367627744715</v>
+        <v>0.08572106405535475</v>
       </c>
       <c r="J11" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="K11" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01490281432071716</v>
+        <v>0.01626471379957839</v>
       </c>
       <c r="M11" t="n">
-        <v>4.038681742033133</v>
+        <v>4.029964290722686</v>
       </c>
       <c r="N11" t="n">
-        <v>26.92785623731752</v>
+        <v>26.84522409389065</v>
       </c>
       <c r="O11" t="n">
-        <v>5.189205742434725</v>
+        <v>5.181237699033953</v>
       </c>
       <c r="P11" t="n">
-        <v>320.8593998969345</v>
+        <v>320.8252385384347</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -27350,7 +27506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L496"/>
+  <dimension ref="A1:L499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58053,6 +58209,192 @@
         </is>
       </c>
     </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:03+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>-46.77741517053408,168.53035731125348</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>-46.776536379936985,168.52932608223114</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>-46.77668213546556,168.52843425489488</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>-46.77691974895807,168.52757135632496</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>-46.77722991759874,168.52676950393067</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>-46.777582853985365,168.52602075097963</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>-46.77798159852514,168.5253210968253</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>-46.77844738604038,168.52471570851446</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>-46.778967918332576,168.52421008887976</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>-46.779518477370644,168.52379377958079</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>-46.777346467075084,168.53034778599476</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>-46.77651399938363,168.52932200133785</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>-46.776649018186816,168.52842518484388</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>-46.776904354167215,168.52756413121597</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>-46.77722057294462,168.5267619360938</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>-46.77757436088108,168.5260115096762</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>-46.777980144663566,168.5253191467864</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>-46.77844537935068,168.5247121831961</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>-46.778963647043206,168.52420087111733</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>-46.77950404434239,168.52376017098848</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>-46.777346467075084,168.53034778599476</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>-46.776507668629485,168.52932084698205</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>-46.77664133497809,168.52842308059346</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>-46.77689776861769,168.52756104047606</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>-46.777211699449154,168.52675474983087</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>-46.77756363653659,168.52599984057682</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>-46.7779684476853,168.52530345784058</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>-46.778434657892504,168.52469334792838</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>-46.77895148642729,168.52417462761358</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>-46.779494041248036,168.52373687791555</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
